--- a/artfynd/A 47035-2022 artfynd.xlsx
+++ b/artfynd/A 47035-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47035-2022 artfynd.xlsx
+++ b/artfynd/A 47035-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16976740</v>
+        <v>16734445</v>
       </c>
       <c r="B2" t="n">
-        <v>96688</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222112</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sädvajaure, NV om Guigovaratjah, vid väg 95, Pi lm</t>
+          <t>Stiepal, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562525</v>
+        <v>559299</v>
       </c>
       <c r="R2" t="n">
-        <v>7377504</v>
+        <v>7380784</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +738,14 @@
           <t>Arjeplog</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>PL-Arj-0125</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-07-19</t>
+          <t>2014-08-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-07-19</t>
+          <t>2014-08-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,35 +756,35 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>högörtsbjörkskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Birgitta Öster</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-mari Sundkvist, Maj-Lis Granström</t>
+          <t>Birgitta Öster, Hans Erik Öster</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104657332</v>
+        <v>55270148</v>
       </c>
       <c r="B3" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,46 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>222467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillviken, Pi lm</t>
+          <t>Stuorsavvon vid camping, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562345.1578992032</v>
+        <v>559586</v>
       </c>
       <c r="R3" t="n">
-        <v>7378008.588523941</v>
+        <v>7382139</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,35 +862,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Rikkärr</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Sture Westerberg, Frida Snell</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104657322</v>
+        <v>5268287</v>
       </c>
       <c r="B4" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98234</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,43 +894,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>222759</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Taggbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Polystichum lonchitis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillviken, Pi lm</t>
+          <t>Sädvajaure, väg 95, SV Guigovaratjah, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562353.4898590008</v>
+        <v>564442</v>
       </c>
       <c r="R4" t="n">
-        <v>7377975.644324012</v>
+        <v>7374561</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,22 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,75 +966,91 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>vägkant med sprängsten</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Umeå-Herbarium UME</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>12-527</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Maj-Lis Granström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2634911</v>
+        <v>120415644</v>
       </c>
       <c r="B5" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219795</v>
+        <v>100127</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Öring</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Salmo trutta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
+          <t>Gujgovárátja 4, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562524.744899151</v>
+        <v>562921</v>
       </c>
       <c r="R5" t="n">
-        <v>7377504.036785915</v>
+        <v>7376326</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,22 +1074,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-07-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-07-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Projekt invasiva fiskarter, Länsstyrelsen Norrbotten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,40 +1095,30 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>vägområde med bäck</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström</t>
+          <t>Andreas Broman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+          <t>Andreas Broman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>Invasiva fiskarter i Norrbotten</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4821531</v>
+        <v>104657338</v>
       </c>
       <c r="B6" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,37 +1126,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
+          <t>Lillviken, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562524.744899151</v>
+        <v>562888</v>
       </c>
       <c r="R6" t="n">
-        <v>7377504.036785915</v>
+        <v>7376308</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,22 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-07-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-07-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,40 +1205,30 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>vägområde med bäck</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2634909</v>
+        <v>104657328</v>
       </c>
       <c r="B7" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99049</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,37 +1236,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219795</v>
+        <v>219794</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sädvajaure, OSO Långudden, Pi lm</t>
+          <t>Lillviken, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575667.0020946923</v>
+        <v>562923</v>
       </c>
       <c r="R7" t="n">
-        <v>7369839.538283391</v>
+        <v>7376403</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1348,22 +1299,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2012-07-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2012-07-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,24 +1315,3645 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>extremrikkärr, källdråg</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2634911</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>562525</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7377504</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>vägområde med bäck</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104657323</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lillviken, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>562334</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7377981</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104657326</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lillviken, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>562336</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7377983</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104657332</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lillviken, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>562345</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7378008</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>104657336</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lillviken, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>562888</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7376308</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104657350</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lillviken, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>560655</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7379029</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2464259</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>562348</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7377950</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>rik vägkant</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104657329</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lillviken, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>562912</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7376357</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4400315</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>562345</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7378001</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>vägdike med rinnande vatten</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104657322</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lillviken, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>562354</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7377976</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4547964</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>562525</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7377504</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>vägområde med bäck</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4821531</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>562525</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7377504</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>vägområde med bäck</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>104657331</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97982</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222424</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium alpinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lillviken, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>561066</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7378896</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5988270</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>562348</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7377950</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>rik vägkant</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5996034</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99121</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>223614</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vanlig brudsporre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>562348</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7377950</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>rik vägkant</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6197350</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97991</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>224359</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Finnlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum subsp. montellii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Kukkonen) Karlsson</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stiehpaltjåhkkås S-sluttning mot Silvervägen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>561116</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7378866</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2011-08-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2011-08-22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ganska riklig.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Vägdike</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6208559</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97984</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>224362</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Nordlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. alpestre</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartm.) Á. Löve &amp; D. Löve</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>562348</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7377950</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>rik vägkant</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>55262725</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ballasluokta, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>566754</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7375334</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2015-08-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2015-08-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Artrik vägslänt</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>55262745</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98030</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ballasluokta, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>566754</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7375334</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2015-08-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2015-08-18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Artrik vägslänt</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>55262737</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ballasluokta, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>566754</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7375334</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2015-08-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2015-08-18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Artrik vägslänt</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>5988022</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Väg 95 Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>566827</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7375325</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2012-07-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2012-07-18</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>55262732</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ballasluokta, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>566754</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7375334</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2015-08-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2015-08-18</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Artrik vägslänt</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>55262731</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97974</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>224360</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gul groddlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Huperzia arctica</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Grossh. ex Tolm.) Sipliv.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ballasluokta, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>566754</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7375334</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2015-08-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2015-08-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Artrik vägslänt</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2634905</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Väg 95 Ballastviken Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>568829</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7374390</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2012-07-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2012-07-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Vägkant m bäck</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2463903</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Väg 95 Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>569242</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7373630</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2012-07-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2012-07-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Vägkant m blött dike</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>4250761</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Väg 95 Ballastviken Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>568829</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7374390</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2012-07-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2012-07-18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Vägkant m bäck</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>5996030</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99121</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>223614</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vanlig brudsporre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Väg 95 Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>569242</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7373630</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2012-07-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2012-07-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Vägkant m blött dike</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2410666</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sädvajaure, OSO Långudden, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>575731</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7369800</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>vägslänt</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
           <t>Mats G Nettelbladt</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>Mats G Nettelbladt, Charlotte Nordgren</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2634909</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sädvajaure, OSO Långudden, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>575667</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7369840</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>extremrikkärr, källdråg</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mats G Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mats G Nettelbladt, Charlotte Nordgren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>104657363</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>S Lillviken-Jutis, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>575724</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7369831</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>104657354</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>S Lillviken-Jutis, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>574579</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7370175</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>104657368</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>S Lillviken-Jutis, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>575804</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7369810</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>17319711</v>
+      </c>
+      <c r="B40" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Riebrebuoda vid väg 95, Silvervägen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>573926</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7370689</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2014-07-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2014-07-04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>17319708</v>
+      </c>
+      <c r="B41" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Riebrebuoda vid väg 95, Silvervägen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>573926</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7370689</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2014-07-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2014-07-04</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
         <is>
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>

--- a/artfynd/A 47035-2022 artfynd.xlsx
+++ b/artfynd/A 47035-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16734445</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55270148</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
           <t>Invasiva fiskarter i Norrbotten</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120415644</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657338</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657328</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657336</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657329</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2634911</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1647,6 +1692,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657323</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657326</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1867,6 +1922,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657332</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1977,6 +2037,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657350</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2083,6 +2148,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2464259</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2189,6 +2259,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4400315</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2299,6 +2374,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657322</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2405,6 +2485,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4547964</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2511,6 +2596,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4821531</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2621,6 +2711,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657331</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2723,6 +2818,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5988270</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2825,6 +2925,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5996034</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2933,6 +3038,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6197350</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3039,6 +3149,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6208559</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3141,6 +3256,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55262725</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3243,6 +3363,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55262745</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3345,6 +3470,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55262737</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3466,6 +3596,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5268287</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3573,6 +3708,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5988022</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3671,6 +3811,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55262732</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3773,6 +3918,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55262731</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3884,6 +4034,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2634905</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3995,6 +4150,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2463903</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4101,6 +4261,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4250761</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4208,6 +4373,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5996030</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4314,6 +4484,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2410666</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4420,6 +4595,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2634909</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4530,6 +4710,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657363</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4640,6 +4825,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657354</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4748,6 +4938,11 @@
       <c r="AY39" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657368</t>
         </is>
       </c>
     </row>
@@ -4854,6 +5049,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17319711</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4958,8 +5158,55 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17319708</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>